--- a/语流变化.xlsx
+++ b/语流变化.xlsx
@@ -1,41 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tastror/my/code/zsaanhehhehhu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Program Devs\Zsaanhe'e'u\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C3DF29-7172-B04C-8FBA-477CFCBA9BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A240AAC-3D24-4212-BA6D-2FCDCCCAF35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17220" yWindow="2800" windowWidth="28040" windowHeight="18700" xr2:uid="{5E018682-C7BE-1949-B62A-102F86B88A8D}"/>
+    <workbookView xWindow="1320" yWindow="2136" windowWidth="23040" windowHeight="12852" xr2:uid="{5E018682-C7BE-1949-B62A-102F86B88A8D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="非动宾短语" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="53">
   <si>
     <t>ā</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -57,90 +47,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>āà</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aqà</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áqà</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>āā</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áā</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aqā</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aqá</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áqá</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>àaq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aqaq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áqaq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>àáq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ááq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>aqáq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áqáq</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>āá: 1-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áá: 1-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áà: 1-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>àá: 5-1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>àā: 3-4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>áaq: 1-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>āáq: 32-4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -149,7 +59,193 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>āaq: 1-5?</t>
+    <t>áá: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>áà: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>áaq: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>àā: 5-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>āá: 32-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>āà: 32-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>āā: 32-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>āaq: 32-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>àaq: 5-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>àáq: 5-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>áā: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ááq: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqà: 4-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqā: 4-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqá: 4-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqaq: 4-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqáq: 4-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>松江/金山/当心</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>青浦/需要</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>浦东/宝山</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无锡/乘客</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长宁/徐汇/闵行/崇明/奉贤/闲话/谢谢/后门/就是</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普陀/准备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>上海/黄浦/杨浦/事体/有点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>嘉定/帮助/再会</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aqā: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>静安/虹口/市区/常州/下车/辰光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配合/快乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>áqà: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>áqaq: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>áqáq: 2-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生日/周末</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>核对</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>适意/客气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>áqá: 2-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="20"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实在/服务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>请客/晓得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>昨日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>学生/弗去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出示/客人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑雪/日出</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -157,7 +253,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -176,6 +272,32 @@
     <font>
       <sz val="20"/>
       <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="20"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -202,12 +324,21 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -523,13 +654,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D60C45B-F158-B548-96CE-79A87118330B}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="15.83203125" defaultRowHeight="30" customHeight="1"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="30.6328125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="15.83203125" style="1"/>
+    <col min="1" max="1" width="5.6328125" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="30.6328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
+    <row r="1" spans="1:6" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
@@ -546,104 +678,216 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="30" customHeight="1">
+    <row r="2" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="30" customHeight="1">
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30" customHeight="1">
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30" customHeight="1">
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="30" customHeight="1">
+      <c r="B5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>19</v>
+      <c r="B6" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
